--- a/output/pdf_financials_xlsx/PIF.xlsx
+++ b/output/pdf_financials_xlsx/PIF.xlsx
@@ -2709,10 +2709,10 @@
         <v>33.38</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>62.327</v>
+        <v>2.111</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>100.819</v>
+        <v>2.889</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>4.045</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/pdf_financials_xlsx/PIF.xlsx
+++ b/output/pdf_financials_xlsx/PIF.xlsx
@@ -941,22 +941,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.257705</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.210381</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.07591100000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.286153</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.535588</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>1.581</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -964,22 +964,22 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.314</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.374</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.886</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>2.855</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>3.652</v>
       </c>
     </row>
     <row r="13">
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-42.710847</v>
+        <v>-42.968552</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-12.093805</v>
+        <v>-12.304186</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-33.616232</v>
+        <v>-33.692143</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.280434</v>
+        <v>2.994281</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>9.927274000000001</v>
+        <v>9.391686</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>24.341</v>
+        <v>22.76</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>38.984</v>
+        <v>38.67</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4.418</v>
+        <v>4.044</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.969</v>
+        <v>0.292</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>6.365</v>
+        <v>4.479</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.847</v>
+        <v>-2.008</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -1825,22 +1825,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-42.710847</v>
+        <v>-42.968552</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-12.093805</v>
+        <v>-12.304186</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-33.616232</v>
+        <v>-33.692143</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.280434</v>
+        <v>2.994281</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>31.659669</v>
+        <v>31.124081</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>47.243576</v>
+        <v>45.662576</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1848,19 +1848,19 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>63.73</v>
+        <v>63.416</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>30.8</v>
+        <v>30.426</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>26.561</v>
+        <v>25.884</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>35.533</v>
+        <v>33.647</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>30.283</v>
+        <v>27.428</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -1875,22 +1875,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-92.42760677146147</v>
+        <v>-92.985288439611</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-25.09939783303239</v>
+        <v>-25.53602108067953</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-67.03206894859541</v>
+        <v>-67.18343842349542</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6.001619564272007</v>
+        <v>5.478096931847417</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>52.67253083658711</v>
+        <v>51.78146733729071</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>68.64404277577589</v>
+        <v>66.34687899569917</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>85.29175588865097</v>
+        <v>84.87152034261241</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>51.74992019086984</v>
+        <v>51.12152830283785</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -2044,31 +2044,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>22.549994</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>15.29154</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>61.592219</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>45.739008</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>37.21712</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>37.809</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>32.597</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>60.058</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>35.325</v>
@@ -2136,31 +2136,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>22.549994</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>15.29154</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>61.592219</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>45.739008</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>37.21712</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>37.809</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>32.597</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>60.058</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>35.325</v>
@@ -2688,28 +2688,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>29.33833</v>
+        <v>6.788336</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>16.440251</v>
+        <v>1.148711</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>62.453948</v>
+        <v>0.861729</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46.658456</v>
+        <v>0.919448</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>38.005096</v>
+        <v>0.787976</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>38.873</v>
+        <v>1.064</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>33.38</v>
+        <v>0.783</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.111</v>
+        <v>2.269</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>2.889</v>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -32645,7 +32645,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -33285,7 +33285,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -34158,7 +34158,11 @@
           <t>General and administrative expenses 7(b)</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -34385,7 +34389,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E342" s="5" t="n">
@@ -36433,7 +36437,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -37648,7 +37652,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -42956,7 +42960,11 @@
           <t>Other general and adminstrative expenses</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PIF.xlsx
+++ b/output/pdf_financials_xlsx/PIF.xlsx
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.09629500000000001</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.98207</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.5278969999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.241946</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.273436</v>
+        <v>1.65101</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1.578021</v>
+        <v>2.036097</v>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0</v>
@@ -845,22 +845,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.09629500000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.98207</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.5278969999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.241946</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.678164</v>
+        <v>2.055738</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.995506</v>
+        <v>2.453582</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -871,13 +871,13 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0</v>
@@ -34241,7 +34241,11 @@
           <t>Other operating costs</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -34258,13 +34262,13 @@
         </is>
       </c>
       <c r="H340" s="5" t="n">
-        <v>-0.241946</v>
+        <v>0.241946</v>
       </c>
       <c r="I340" s="5" t="n">
-        <v>-0.377574</v>
+        <v>0.377574</v>
       </c>
       <c r="J340" s="5" t="n">
-        <v>-0.458076</v>
+        <v>0.458076</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
@@ -34277,13 +34281,13 @@
         </is>
       </c>
       <c r="M340" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="N340" s="5" t="n">
-        <v>-0.788</v>
+        <v>0.788</v>
       </c>
       <c r="O340" s="5" t="n">
-        <v>-0.021</v>
+        <v>0.021</v>
       </c>
       <c r="P340" t="inlineStr">
         <is>
@@ -46007,18 +46011,22 @@
           <t>Other operating costs 6</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E488" s="5" t="n">
         <v>0.09629500000000001</v>
       </c>
       <c r="F488" s="5" t="n">
-        <v>-0.98207</v>
+        <v>0.98207</v>
       </c>
       <c r="G488" s="5" t="n">
-        <v>-0.5278969999999999</v>
+        <v>0.5278969999999999</v>
       </c>
       <c r="H488" s="5" t="n">
-        <v>-0.241946</v>
+        <v>0.241946</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
